--- a/data-source/元素熔炉数据.xlsx
+++ b/data-source/元素熔炉数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6915BB7-D573-4512-9928-CD6FCBABADA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D21FFE-701C-4E89-8F56-6ADBEE1AC80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{AF2E5857-F478-439B-BD69-977BE72B6D2F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>建造材料</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>火把*1 小型火焰精华*5 硝酸钾*1 碎铜片*20</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>需组装；修道院</t>
   </si>
 </sst>
 </file>
@@ -700,6 +706,7 @@
     <col min="7" max="7" width="45.06640625" customWidth="1"/>
     <col min="8" max="8" width="32.33203125" customWidth="1"/>
     <col min="9" max="9" width="17.59765625" customWidth="1"/>
+    <col min="10" max="10" width="18.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
@@ -730,7 +737,9 @@
       <c r="I1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1"/>
+      <c r="J1" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -767,7 +776,9 @@
       <c r="I2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="J2" s="10" t="s">
+        <v>47</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -796,7 +807,7 @@
       <c r="I3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="1"/>
+      <c r="J3" s="10"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -825,7 +836,7 @@
       <c r="I4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J4" s="1"/>
+      <c r="J4" s="10"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -854,7 +865,7 @@
       <c r="I5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="1"/>
+      <c r="J5" s="10"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -883,7 +894,7 @@
       <c r="I6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1"/>
+      <c r="J6" s="10"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -912,7 +923,7 @@
       <c r="I7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="10"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -941,7 +952,7 @@
       <c r="I8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="10"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -970,7 +981,7 @@
       <c r="I9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="10"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -1376,11 +1387,12 @@
       <c r="Q30" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A2:A9"/>
     <mergeCell ref="B2:B9"/>
     <mergeCell ref="D2:D9"/>
     <mergeCell ref="C2:C9"/>
+    <mergeCell ref="J2:J9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
